--- a/site/docs/source/TPFDD-Ops-Sequence.xlsx
+++ b/site/docs/source/TPFDD-Ops-Sequence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OPORDs, FRAGOs, WARNOs\RGT\OPORDs\2026\RO 26-05-01 TNMAN-26\TNMAN-26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE147F5-0661-444D-B0B1-45C8A9A06F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4E4DCA-0BFA-4EB4-B604-F90E4A4EABB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="95">
   <si>
     <t>0600</t>
   </si>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t>Staging</t>
-  </si>
-  <si>
-    <t>Rest</t>
   </si>
   <si>
     <t>Prepare</t>
@@ -1090,21 +1087,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1135,21 +1117,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1175,34 +1142,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1492,6 +1431,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1615,35 +1608,143 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1669,11 +1770,20 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1681,163 +1791,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1848,6 +1820,27 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2147,108 +2140,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:94" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="115" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="40">
+      <c r="A1" s="108" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="101">
         <v>46155</v>
       </c>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="41"/>
-      <c r="U1" s="41"/>
-      <c r="V1" s="41"/>
-      <c r="W1" s="41"/>
-      <c r="X1" s="41"/>
-      <c r="Y1" s="41"/>
-      <c r="Z1" s="41"/>
-      <c r="AA1" s="41"/>
-      <c r="AB1" s="41"/>
-      <c r="AC1" s="41"/>
-      <c r="AD1" s="41"/>
-      <c r="AE1" s="41"/>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="40">
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="103"/>
+      <c r="AG1" s="101">
         <v>46156</v>
       </c>
-      <c r="AH1" s="41"/>
-      <c r="AI1" s="41"/>
-      <c r="AJ1" s="41"/>
-      <c r="AK1" s="41"/>
-      <c r="AL1" s="41"/>
-      <c r="AM1" s="41"/>
-      <c r="AN1" s="41"/>
-      <c r="AO1" s="41"/>
-      <c r="AP1" s="41"/>
-      <c r="AQ1" s="41"/>
-      <c r="AR1" s="41"/>
-      <c r="AS1" s="41"/>
-      <c r="AT1" s="41"/>
-      <c r="AU1" s="41"/>
-      <c r="AV1" s="41"/>
-      <c r="AW1" s="41"/>
-      <c r="AX1" s="41"/>
-      <c r="AY1" s="41"/>
-      <c r="AZ1" s="41"/>
-      <c r="BA1" s="41"/>
-      <c r="BB1" s="41"/>
-      <c r="BC1" s="41"/>
-      <c r="BD1" s="41"/>
-      <c r="BE1" s="41"/>
-      <c r="BF1" s="41"/>
-      <c r="BG1" s="41"/>
-      <c r="BH1" s="41"/>
-      <c r="BI1" s="41"/>
-      <c r="BJ1" s="42"/>
-      <c r="BK1" s="40">
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
+      <c r="AP1" s="102"/>
+      <c r="AQ1" s="102"/>
+      <c r="AR1" s="102"/>
+      <c r="AS1" s="102"/>
+      <c r="AT1" s="102"/>
+      <c r="AU1" s="102"/>
+      <c r="AV1" s="102"/>
+      <c r="AW1" s="102"/>
+      <c r="AX1" s="102"/>
+      <c r="AY1" s="102"/>
+      <c r="AZ1" s="102"/>
+      <c r="BA1" s="102"/>
+      <c r="BB1" s="102"/>
+      <c r="BC1" s="102"/>
+      <c r="BD1" s="102"/>
+      <c r="BE1" s="102"/>
+      <c r="BF1" s="102"/>
+      <c r="BG1" s="102"/>
+      <c r="BH1" s="102"/>
+      <c r="BI1" s="102"/>
+      <c r="BJ1" s="103"/>
+      <c r="BK1" s="101">
         <v>46157</v>
       </c>
-      <c r="BL1" s="41"/>
-      <c r="BM1" s="41"/>
-      <c r="BN1" s="41"/>
-      <c r="BO1" s="41"/>
-      <c r="BP1" s="41"/>
-      <c r="BQ1" s="41"/>
-      <c r="BR1" s="41"/>
-      <c r="BS1" s="41"/>
-      <c r="BT1" s="41"/>
-      <c r="BU1" s="41"/>
-      <c r="BV1" s="41"/>
-      <c r="BW1" s="41"/>
-      <c r="BX1" s="41"/>
-      <c r="BY1" s="41"/>
-      <c r="BZ1" s="41"/>
-      <c r="CA1" s="41"/>
-      <c r="CB1" s="41"/>
-      <c r="CC1" s="41"/>
-      <c r="CD1" s="41"/>
-      <c r="CE1" s="41"/>
-      <c r="CF1" s="41"/>
-      <c r="CG1" s="41"/>
-      <c r="CH1" s="41"/>
-      <c r="CI1" s="41"/>
-      <c r="CJ1" s="41"/>
-      <c r="CK1" s="41"/>
-      <c r="CL1" s="41"/>
-      <c r="CM1" s="41"/>
-      <c r="CN1" s="42"/>
+      <c r="BL1" s="102"/>
+      <c r="BM1" s="102"/>
+      <c r="BN1" s="102"/>
+      <c r="BO1" s="102"/>
+      <c r="BP1" s="102"/>
+      <c r="BQ1" s="102"/>
+      <c r="BR1" s="102"/>
+      <c r="BS1" s="102"/>
+      <c r="BT1" s="102"/>
+      <c r="BU1" s="102"/>
+      <c r="BV1" s="102"/>
+      <c r="BW1" s="102"/>
+      <c r="BX1" s="102"/>
+      <c r="BY1" s="102"/>
+      <c r="BZ1" s="102"/>
+      <c r="CA1" s="102"/>
+      <c r="CB1" s="102"/>
+      <c r="CC1" s="102"/>
+      <c r="CD1" s="102"/>
+      <c r="CE1" s="102"/>
+      <c r="CF1" s="102"/>
+      <c r="CG1" s="102"/>
+      <c r="CH1" s="102"/>
+      <c r="CI1" s="102"/>
+      <c r="CJ1" s="102"/>
+      <c r="CK1" s="102"/>
+      <c r="CL1" s="102"/>
+      <c r="CM1" s="102"/>
+      <c r="CN1" s="103"/>
       <c r="CO1" s="28">
         <v>46158</v>
       </c>
@@ -2257,104 +2250,104 @@
       </c>
     </row>
     <row r="2" spans="1:94" s="16" customFormat="1" ht="13.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="116"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="47" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
-      <c r="AA2" s="43"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="43"/>
-      <c r="AD2" s="43"/>
-      <c r="AE2" s="43"/>
-      <c r="AF2" s="44"/>
-      <c r="AG2" s="47" t="s">
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="104"/>
+      <c r="R2" s="104"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="104"/>
+      <c r="U2" s="104"/>
+      <c r="V2" s="104"/>
+      <c r="W2" s="104"/>
+      <c r="X2" s="104"/>
+      <c r="Y2" s="104"/>
+      <c r="Z2" s="104"/>
+      <c r="AA2" s="104"/>
+      <c r="AB2" s="104"/>
+      <c r="AC2" s="104"/>
+      <c r="AD2" s="104"/>
+      <c r="AE2" s="104"/>
+      <c r="AF2" s="105"/>
+      <c r="AG2" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="AH2" s="43"/>
-      <c r="AI2" s="43"/>
-      <c r="AJ2" s="43"/>
-      <c r="AK2" s="43"/>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="43"/>
-      <c r="AN2" s="43"/>
-      <c r="AO2" s="43"/>
-      <c r="AP2" s="43"/>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="43"/>
-      <c r="AS2" s="43"/>
-      <c r="AT2" s="43"/>
-      <c r="AU2" s="43"/>
-      <c r="AV2" s="43"/>
-      <c r="AW2" s="43"/>
-      <c r="AX2" s="43"/>
-      <c r="AY2" s="43"/>
-      <c r="AZ2" s="43"/>
-      <c r="BA2" s="43"/>
-      <c r="BB2" s="43"/>
-      <c r="BC2" s="43"/>
-      <c r="BD2" s="43"/>
-      <c r="BE2" s="43"/>
-      <c r="BF2" s="43"/>
-      <c r="BG2" s="43"/>
-      <c r="BH2" s="43"/>
-      <c r="BI2" s="43"/>
-      <c r="BJ2" s="44"/>
-      <c r="BK2" s="43" t="s">
+      <c r="AH2" s="104"/>
+      <c r="AI2" s="104"/>
+      <c r="AJ2" s="104"/>
+      <c r="AK2" s="104"/>
+      <c r="AL2" s="104"/>
+      <c r="AM2" s="104"/>
+      <c r="AN2" s="104"/>
+      <c r="AO2" s="104"/>
+      <c r="AP2" s="104"/>
+      <c r="AQ2" s="104"/>
+      <c r="AR2" s="104"/>
+      <c r="AS2" s="104"/>
+      <c r="AT2" s="104"/>
+      <c r="AU2" s="104"/>
+      <c r="AV2" s="104"/>
+      <c r="AW2" s="104"/>
+      <c r="AX2" s="104"/>
+      <c r="AY2" s="104"/>
+      <c r="AZ2" s="104"/>
+      <c r="BA2" s="104"/>
+      <c r="BB2" s="104"/>
+      <c r="BC2" s="104"/>
+      <c r="BD2" s="104"/>
+      <c r="BE2" s="104"/>
+      <c r="BF2" s="104"/>
+      <c r="BG2" s="104"/>
+      <c r="BH2" s="104"/>
+      <c r="BI2" s="104"/>
+      <c r="BJ2" s="105"/>
+      <c r="BK2" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="BL2" s="43"/>
-      <c r="BM2" s="43"/>
-      <c r="BN2" s="43"/>
-      <c r="BO2" s="43"/>
-      <c r="BP2" s="43"/>
-      <c r="BQ2" s="43"/>
-      <c r="BR2" s="43"/>
-      <c r="BS2" s="43"/>
-      <c r="BT2" s="43"/>
-      <c r="BU2" s="43"/>
-      <c r="BV2" s="43"/>
-      <c r="BW2" s="43"/>
-      <c r="BX2" s="43"/>
-      <c r="BY2" s="43"/>
-      <c r="BZ2" s="43"/>
-      <c r="CA2" s="43"/>
-      <c r="CB2" s="43"/>
-      <c r="CC2" s="43"/>
-      <c r="CD2" s="43"/>
-      <c r="CE2" s="43"/>
-      <c r="CF2" s="43"/>
-      <c r="CG2" s="43"/>
-      <c r="CH2" s="43"/>
-      <c r="CI2" s="43"/>
-      <c r="CJ2" s="43"/>
-      <c r="CK2" s="43"/>
-      <c r="CL2" s="43"/>
-      <c r="CM2" s="43"/>
-      <c r="CN2" s="44"/>
+      <c r="BL2" s="104"/>
+      <c r="BM2" s="104"/>
+      <c r="BN2" s="104"/>
+      <c r="BO2" s="104"/>
+      <c r="BP2" s="104"/>
+      <c r="BQ2" s="104"/>
+      <c r="BR2" s="104"/>
+      <c r="BS2" s="104"/>
+      <c r="BT2" s="104"/>
+      <c r="BU2" s="104"/>
+      <c r="BV2" s="104"/>
+      <c r="BW2" s="104"/>
+      <c r="BX2" s="104"/>
+      <c r="BY2" s="104"/>
+      <c r="BZ2" s="104"/>
+      <c r="CA2" s="104"/>
+      <c r="CB2" s="104"/>
+      <c r="CC2" s="104"/>
+      <c r="CD2" s="104"/>
+      <c r="CE2" s="104"/>
+      <c r="CF2" s="104"/>
+      <c r="CG2" s="104"/>
+      <c r="CH2" s="104"/>
+      <c r="CI2" s="104"/>
+      <c r="CJ2" s="104"/>
+      <c r="CK2" s="104"/>
+      <c r="CL2" s="104"/>
+      <c r="CM2" s="104"/>
+      <c r="CN2" s="105"/>
       <c r="CO2" s="19" t="s">
         <v>33</v>
       </c>
@@ -2363,570 +2356,570 @@
       </c>
     </row>
     <row r="3" spans="1:94" s="17" customFormat="1" ht="14.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="117"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="79" t="s">
+      <c r="A3" s="110"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="79" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="79" t="s">
+      <c r="H3" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="79" t="s">
+      <c r="J3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="79" t="s">
+      <c r="K3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="79" t="s">
+      <c r="L3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="79" t="s">
+      <c r="M3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="79" t="s">
+      <c r="N3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="79" t="s">
+      <c r="O3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="79" t="s">
+      <c r="P3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="79" t="s">
+      <c r="Q3" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="79" t="s">
+      <c r="R3" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="79" t="s">
+      <c r="S3" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="79" t="s">
+      <c r="T3" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="79" t="s">
+      <c r="U3" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="79" t="s">
+      <c r="V3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="79" t="s">
+      <c r="W3" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="79" t="s">
+      <c r="X3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="Y3" s="79" t="s">
+      <c r="Y3" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="Z3" s="79" t="s">
+      <c r="Z3" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="AA3" s="79" t="s">
+      <c r="AA3" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="AB3" s="79" t="s">
+      <c r="AB3" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AC3" s="79" t="s">
+      <c r="AC3" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="AD3" s="79" t="s">
+      <c r="AD3" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AE3" s="79" t="s">
+      <c r="AE3" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="AF3" s="80" t="s">
+      <c r="AF3" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="AG3" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="79" t="s">
+      <c r="AG3" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="AJ3" s="79" t="s">
+      <c r="AJ3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="AK3" s="79" t="s">
+      <c r="AK3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="AL3" s="79" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM3" s="79" t="s">
+      <c r="AL3" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="AN3" s="79" t="s">
+      <c r="AN3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="AO3" s="79" t="s">
+      <c r="AO3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="AP3" s="79" t="s">
+      <c r="AP3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="AQ3" s="79" t="s">
+      <c r="AQ3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="AR3" s="79" t="s">
+      <c r="AR3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="AS3" s="79" t="s">
+      <c r="AS3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="AT3" s="79" t="s">
+      <c r="AT3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="AU3" s="79" t="s">
+      <c r="AU3" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="AV3" s="79" t="s">
+      <c r="AV3" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="AW3" s="79" t="s">
+      <c r="AW3" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="AX3" s="79" t="s">
+      <c r="AX3" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="AY3" s="79" t="s">
+      <c r="AY3" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="AZ3" s="79" t="s">
+      <c r="AZ3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="BA3" s="79" t="s">
+      <c r="BA3" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="BB3" s="79" t="s">
+      <c r="BB3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="BC3" s="79" t="s">
+      <c r="BC3" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="BD3" s="79" t="s">
+      <c r="BD3" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="BE3" s="79" t="s">
+      <c r="BE3" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="BF3" s="79" t="s">
+      <c r="BF3" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="BG3" s="79" t="s">
+      <c r="BG3" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="BH3" s="79" t="s">
+      <c r="BH3" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="BI3" s="79" t="s">
+      <c r="BI3" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="BJ3" s="80" t="s">
+      <c r="BJ3" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="BK3" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="BL3" s="79" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM3" s="79" t="s">
+      <c r="BK3" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="BN3" s="79" t="s">
+      <c r="BN3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="BO3" s="79" t="s">
+      <c r="BO3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="BP3" s="79" t="s">
-        <v>5</v>
-      </c>
-      <c r="BQ3" s="79" t="s">
+      <c r="BP3" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="BQ3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="BR3" s="79" t="s">
+      <c r="BR3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="BS3" s="79" t="s">
+      <c r="BS3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="BT3" s="79" t="s">
+      <c r="BT3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="BU3" s="79" t="s">
+      <c r="BU3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="BV3" s="79" t="s">
+      <c r="BV3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="BW3" s="79" t="s">
+      <c r="BW3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="BX3" s="79" t="s">
+      <c r="BX3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="BY3" s="79" t="s">
+      <c r="BY3" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="BZ3" s="79" t="s">
+      <c r="BZ3" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="CA3" s="79" t="s">
+      <c r="CA3" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="CB3" s="79" t="s">
+      <c r="CB3" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="CC3" s="79" t="s">
+      <c r="CC3" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="CD3" s="79" t="s">
+      <c r="CD3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="CE3" s="79" t="s">
+      <c r="CE3" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="CF3" s="79" t="s">
+      <c r="CF3" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="CG3" s="79" t="s">
+      <c r="CG3" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="CH3" s="79" t="s">
+      <c r="CH3" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="CI3" s="79" t="s">
+      <c r="CI3" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="CJ3" s="79" t="s">
+      <c r="CJ3" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="CK3" s="79" t="s">
+      <c r="CK3" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="CL3" s="79" t="s">
+      <c r="CL3" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="CM3" s="79" t="s">
+      <c r="CM3" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="CN3" s="80" t="s">
+      <c r="CN3" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="CO3" s="81"/>
-      <c r="CP3" s="82"/>
+      <c r="CO3" s="53"/>
+      <c r="CP3" s="54"/>
     </row>
     <row r="4" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A4" s="73" t="s">
+      <c r="A4" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="83">
+      <c r="B4" s="55">
         <v>11</v>
       </c>
-      <c r="C4" s="84">
-        <v>0</v>
-      </c>
-      <c r="D4" s="84">
-        <v>0</v>
-      </c>
-      <c r="E4" s="84">
-        <v>0</v>
-      </c>
-      <c r="F4" s="84">
-        <v>0</v>
-      </c>
-      <c r="G4" s="84">
-        <v>0</v>
-      </c>
-      <c r="H4" s="84">
-        <v>0</v>
-      </c>
-      <c r="I4" s="85">
+      <c r="C4" s="56">
+        <v>0</v>
+      </c>
+      <c r="D4" s="56">
+        <v>0</v>
+      </c>
+      <c r="E4" s="56">
+        <v>0</v>
+      </c>
+      <c r="F4" s="56">
+        <v>0</v>
+      </c>
+      <c r="G4" s="56">
+        <v>0</v>
+      </c>
+      <c r="H4" s="56">
+        <v>0</v>
+      </c>
+      <c r="I4" s="57">
         <v>11</v>
       </c>
-      <c r="J4" s="85">
+      <c r="J4" s="57">
         <v>11</v>
       </c>
-      <c r="K4" s="86">
+      <c r="K4" s="58">
         <v>11</v>
       </c>
-      <c r="L4" s="86">
+      <c r="L4" s="58">
         <v>11</v>
       </c>
-      <c r="M4" s="87">
+      <c r="M4" s="59">
         <v>11</v>
       </c>
-      <c r="N4" s="87">
+      <c r="N4" s="59">
         <v>11</v>
       </c>
-      <c r="O4" s="88">
+      <c r="O4" s="60">
         <v>11</v>
       </c>
-      <c r="P4" s="88">
+      <c r="P4" s="60">
         <v>11</v>
       </c>
-      <c r="Q4" s="88">
+      <c r="Q4" s="60">
         <v>11</v>
       </c>
-      <c r="R4" s="89">
+      <c r="R4" s="61">
         <v>11</v>
       </c>
-      <c r="S4" s="89">
+      <c r="S4" s="61">
         <v>11</v>
       </c>
-      <c r="T4" s="89">
+      <c r="T4" s="61">
         <v>11</v>
       </c>
-      <c r="U4" s="89">
+      <c r="U4" s="61">
         <v>11</v>
       </c>
-      <c r="V4" s="90">
+      <c r="V4" s="62">
         <v>11</v>
       </c>
-      <c r="W4" s="90">
+      <c r="W4" s="62">
         <v>11</v>
       </c>
-      <c r="X4" s="90">
+      <c r="X4" s="62">
         <v>11</v>
       </c>
-      <c r="Y4" s="90">
+      <c r="Y4" s="62">
         <v>11</v>
       </c>
-      <c r="Z4" s="90">
+      <c r="Z4" s="62">
         <v>11</v>
       </c>
-      <c r="AA4" s="90">
+      <c r="AA4" s="62">
         <v>11</v>
       </c>
-      <c r="AB4" s="90">
+      <c r="AB4" s="62">
         <v>11</v>
       </c>
-      <c r="AC4" s="90">
+      <c r="AC4" s="62">
         <v>11</v>
       </c>
-      <c r="AD4" s="90">
+      <c r="AD4" s="62">
         <v>11</v>
       </c>
-      <c r="AE4" s="90">
+      <c r="AE4" s="62">
         <v>11</v>
       </c>
-      <c r="AF4" s="90">
+      <c r="AF4" s="62">
         <v>11</v>
       </c>
-      <c r="AG4" s="90">
+      <c r="AG4" s="62">
         <v>11</v>
       </c>
-      <c r="AH4" s="90">
+      <c r="AH4" s="62">
         <v>11</v>
       </c>
-      <c r="AI4" s="90">
+      <c r="AI4" s="62">
         <v>11</v>
       </c>
-      <c r="AJ4" s="90">
+      <c r="AJ4" s="62">
         <v>11</v>
       </c>
-      <c r="AK4" s="90">
+      <c r="AK4" s="62">
         <v>11</v>
       </c>
-      <c r="AL4" s="90">
+      <c r="AL4" s="62">
         <v>11</v>
       </c>
-      <c r="AM4" s="90">
+      <c r="AM4" s="62">
         <v>11</v>
       </c>
-      <c r="AN4" s="91">
+      <c r="AN4" s="63">
         <v>11</v>
       </c>
-      <c r="AO4" s="90">
+      <c r="AO4" s="62">
         <v>11</v>
       </c>
-      <c r="AP4" s="90">
+      <c r="AP4" s="62">
         <v>11</v>
       </c>
-      <c r="AQ4" s="90">
+      <c r="AQ4" s="62">
         <v>11</v>
       </c>
-      <c r="AR4" s="90">
+      <c r="AR4" s="62">
         <v>11</v>
       </c>
-      <c r="AS4" s="90">
+      <c r="AS4" s="62">
         <v>11</v>
       </c>
-      <c r="AT4" s="90">
+      <c r="AT4" s="62">
         <v>11</v>
       </c>
-      <c r="AU4" s="90">
+      <c r="AU4" s="62">
         <v>11</v>
       </c>
-      <c r="AV4" s="90">
+      <c r="AV4" s="62">
         <v>11</v>
       </c>
-      <c r="AW4" s="90">
+      <c r="AW4" s="62">
         <v>11</v>
       </c>
-      <c r="AX4" s="90">
+      <c r="AX4" s="62">
         <v>11</v>
       </c>
-      <c r="AY4" s="90">
+      <c r="AY4" s="62">
         <v>11</v>
       </c>
-      <c r="AZ4" s="90">
+      <c r="AZ4" s="62">
         <v>11</v>
       </c>
-      <c r="BA4" s="90">
+      <c r="BA4" s="62">
         <v>11</v>
       </c>
-      <c r="BB4" s="90">
+      <c r="BB4" s="62">
         <v>11</v>
       </c>
-      <c r="BC4" s="90">
+      <c r="BC4" s="62">
         <v>11</v>
       </c>
-      <c r="BD4" s="90">
+      <c r="BD4" s="62">
         <v>11</v>
       </c>
-      <c r="BE4" s="90">
+      <c r="BE4" s="62">
         <v>11</v>
       </c>
-      <c r="BF4" s="90">
+      <c r="BF4" s="62">
         <v>11</v>
       </c>
-      <c r="BG4" s="90">
+      <c r="BG4" s="62">
         <v>11</v>
       </c>
-      <c r="BH4" s="90">
+      <c r="BH4" s="62">
         <v>11</v>
       </c>
-      <c r="BI4" s="90">
+      <c r="BI4" s="62">
         <v>11</v>
       </c>
-      <c r="BJ4" s="92">
+      <c r="BJ4" s="64">
         <v>11</v>
       </c>
-      <c r="BK4" s="93">
+      <c r="BK4" s="65">
         <v>11</v>
       </c>
-      <c r="BL4" s="89">
+      <c r="BL4" s="61">
         <v>11</v>
       </c>
-      <c r="BM4" s="89">
+      <c r="BM4" s="61">
         <v>11</v>
       </c>
-      <c r="BN4" s="89">
+      <c r="BN4" s="61">
         <v>11</v>
       </c>
-      <c r="BO4" s="89">
+      <c r="BO4" s="61">
         <v>11</v>
       </c>
-      <c r="BP4" s="89">
+      <c r="BP4" s="61">
         <v>11</v>
       </c>
-      <c r="BQ4" s="88">
+      <c r="BQ4" s="60">
         <v>11</v>
       </c>
-      <c r="BR4" s="88">
+      <c r="BR4" s="60">
         <v>11</v>
       </c>
-      <c r="BS4" s="88">
+      <c r="BS4" s="60">
         <v>11</v>
       </c>
-      <c r="BT4" s="88">
+      <c r="BT4" s="60">
         <v>11</v>
       </c>
-      <c r="BU4" s="88">
+      <c r="BU4" s="60">
         <v>11</v>
       </c>
-      <c r="BV4" s="88">
+      <c r="BV4" s="60">
         <v>11</v>
       </c>
-      <c r="BW4" s="87">
+      <c r="BW4" s="59">
         <v>11</v>
       </c>
-      <c r="BX4" s="87">
+      <c r="BX4" s="59">
         <v>11</v>
       </c>
-      <c r="BY4" s="87">
+      <c r="BY4" s="59">
         <v>11</v>
       </c>
-      <c r="BZ4" s="86">
+      <c r="BZ4" s="58">
         <v>11</v>
       </c>
-      <c r="CA4" s="86">
+      <c r="CA4" s="58">
         <v>11</v>
       </c>
-      <c r="CB4" s="85">
+      <c r="CB4" s="57">
         <v>11</v>
       </c>
-      <c r="CC4" s="85">
+      <c r="CC4" s="57">
         <v>11</v>
       </c>
-      <c r="CD4" s="85">
+      <c r="CD4" s="57">
         <v>11</v>
       </c>
-      <c r="CE4" s="85">
+      <c r="CE4" s="57">
         <v>11</v>
       </c>
-      <c r="CF4" s="94">
-        <v>5</v>
-      </c>
-      <c r="CG4" s="94">
-        <v>5</v>
-      </c>
-      <c r="CH4" s="94">
-        <v>5</v>
-      </c>
-      <c r="CI4" s="94">
-        <v>5</v>
-      </c>
-      <c r="CJ4" s="94">
-        <v>5</v>
-      </c>
-      <c r="CK4" s="94">
-        <v>5</v>
-      </c>
-      <c r="CL4" s="94">
+      <c r="CF4" s="66">
+        <v>5</v>
+      </c>
+      <c r="CG4" s="66">
+        <v>5</v>
+      </c>
+      <c r="CH4" s="66">
+        <v>5</v>
+      </c>
+      <c r="CI4" s="66">
+        <v>5</v>
+      </c>
+      <c r="CJ4" s="66">
+        <v>5</v>
+      </c>
+      <c r="CK4" s="66">
+        <v>5</v>
+      </c>
+      <c r="CL4" s="66">
         <v>4</v>
       </c>
-      <c r="CM4" s="94">
+      <c r="CM4" s="66">
         <v>4</v>
       </c>
-      <c r="CN4" s="94">
+      <c r="CN4" s="66">
         <v>4</v>
       </c>
-      <c r="CO4" s="94">
+      <c r="CO4" s="66">
         <v>3</v>
       </c>
-      <c r="CP4" s="95">
+      <c r="CP4" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A5" s="74" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="96">
+      <c r="A5" s="46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="68">
         <v>5</v>
       </c>
       <c r="C5" s="15">
@@ -3202,15 +3195,15 @@
       <c r="CO5" s="30">
         <v>0</v>
       </c>
-      <c r="CP5" s="97">
+      <c r="CP5" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A6" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="96">
+      <c r="A6" s="46" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="68">
         <v>5</v>
       </c>
       <c r="C6" s="15">
@@ -3470,15 +3463,15 @@
       <c r="CO6" s="30">
         <v>0</v>
       </c>
-      <c r="CP6" s="97">
+      <c r="CP6" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A7" s="74" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="96">
+      <c r="A7" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="68">
         <v>5</v>
       </c>
       <c r="C7" s="15">
@@ -3754,15 +3747,15 @@
       <c r="CO7" s="30">
         <v>0</v>
       </c>
-      <c r="CP7" s="97">
+      <c r="CP7" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A8" s="75" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="96">
+      <c r="A8" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="68">
         <v>5</v>
       </c>
       <c r="C8" s="15">
@@ -4038,15 +4031,15 @@
       <c r="CO8" s="30">
         <v>0</v>
       </c>
-      <c r="CP8" s="97">
+      <c r="CP8" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A9" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="96">
+      <c r="A9" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="68">
         <v>5</v>
       </c>
       <c r="C9" s="15">
@@ -4322,15 +4315,15 @@
       <c r="CO9" s="30">
         <v>0</v>
       </c>
-      <c r="CP9" s="97">
+      <c r="CP9" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A10" s="76" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="96">
+      <c r="A10" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="68">
         <v>5</v>
       </c>
       <c r="C10" s="15">
@@ -4606,15 +4599,15 @@
       <c r="CO10" s="30">
         <v>0</v>
       </c>
-      <c r="CP10" s="97">
+      <c r="CP10" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A11" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="B11" s="96">
+      <c r="A11" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="68">
         <v>5</v>
       </c>
       <c r="C11" s="15">
@@ -4890,15 +4883,15 @@
       <c r="CO11" s="30">
         <v>0</v>
       </c>
-      <c r="CP11" s="97">
+      <c r="CP11" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A12" s="76" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="96">
+      <c r="A12" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="68">
         <v>5</v>
       </c>
       <c r="C12" s="15">
@@ -5174,15 +5167,15 @@
       <c r="CO12" s="30">
         <v>0</v>
       </c>
-      <c r="CP12" s="97">
+      <c r="CP12" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A13" s="76" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="96">
+      <c r="A13" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="68">
         <v>5</v>
       </c>
       <c r="C13" s="15">
@@ -5458,15 +5451,15 @@
       <c r="CO13" s="30">
         <v>0</v>
       </c>
-      <c r="CP13" s="97">
+      <c r="CP13" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A14" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="B14" s="96">
+      <c r="A14" s="48" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="68">
         <v>5</v>
       </c>
       <c r="C14" s="15">
@@ -5742,15 +5735,15 @@
       <c r="CO14" s="30">
         <v>0</v>
       </c>
-      <c r="CP14" s="97">
+      <c r="CP14" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A15" s="76" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="96">
+      <c r="A15" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="68">
         <v>5</v>
       </c>
       <c r="C15" s="15">
@@ -6026,15 +6019,15 @@
       <c r="CO15" s="30">
         <v>0</v>
       </c>
-      <c r="CP15" s="97">
+      <c r="CP15" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A16" s="76" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="96">
+      <c r="A16" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="68">
         <v>5</v>
       </c>
       <c r="C16" s="15">
@@ -6310,15 +6303,15 @@
       <c r="CO16" s="30">
         <v>0</v>
       </c>
-      <c r="CP16" s="97">
+      <c r="CP16" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A17" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="96">
+      <c r="A17" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="68">
         <v>5</v>
       </c>
       <c r="C17" s="15">
@@ -6594,15 +6587,15 @@
       <c r="CO17" s="30">
         <v>0</v>
       </c>
-      <c r="CP17" s="97">
+      <c r="CP17" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A18" s="76" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="96">
+      <c r="A18" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="68">
         <v>5</v>
       </c>
       <c r="C18" s="15">
@@ -6878,15 +6871,15 @@
       <c r="CO18" s="30">
         <v>0</v>
       </c>
-      <c r="CP18" s="97">
+      <c r="CP18" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A19" s="76" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="96">
+      <c r="A19" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="68">
         <v>5</v>
       </c>
       <c r="C19" s="15">
@@ -7162,15 +7155,15 @@
       <c r="CO19" s="30">
         <v>0</v>
       </c>
-      <c r="CP19" s="97">
+      <c r="CP19" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A20" s="76" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="96">
+      <c r="A20" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="68">
         <v>5</v>
       </c>
       <c r="C20" s="15">
@@ -7446,15 +7439,15 @@
       <c r="CO20" s="30">
         <v>0</v>
       </c>
-      <c r="CP20" s="97">
+      <c r="CP20" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A21" s="76" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="96">
+      <c r="A21" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="68">
         <v>5</v>
       </c>
       <c r="C21" s="15">
@@ -7730,15 +7723,15 @@
       <c r="CO21" s="30">
         <v>0</v>
       </c>
-      <c r="CP21" s="97">
+      <c r="CP21" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A22" s="74" t="s">
+      <c r="A22" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="96">
+      <c r="B22" s="68">
         <v>8</v>
       </c>
       <c r="C22" s="15">
@@ -8014,15 +8007,15 @@
       <c r="CO22" s="30">
         <v>0</v>
       </c>
-      <c r="CP22" s="97">
+      <c r="CP22" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A23" s="74" t="s">
+      <c r="A23" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="96">
+      <c r="B23" s="68">
         <v>1</v>
       </c>
       <c r="C23" s="15">
@@ -8298,15 +8291,15 @@
       <c r="CO23" s="30">
         <v>0</v>
       </c>
-      <c r="CP23" s="97">
+      <c r="CP23" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A24" s="74" t="s">
+      <c r="A24" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="96">
+      <c r="B24" s="68">
         <v>1</v>
       </c>
       <c r="C24" s="15">
@@ -8582,15 +8575,15 @@
       <c r="CO24" s="30">
         <v>0</v>
       </c>
-      <c r="CP24" s="97">
+      <c r="CP24" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A25" s="74" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="96">
+      <c r="A25" s="46" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="68">
         <v>1</v>
       </c>
       <c r="C25" s="15">
@@ -8866,15 +8859,15 @@
       <c r="CO25" s="30">
         <v>0</v>
       </c>
-      <c r="CP25" s="97">
+      <c r="CP25" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A26" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="96">
+      <c r="A26" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="68">
         <v>1</v>
       </c>
       <c r="C26" s="15">
@@ -9150,15 +9143,15 @@
       <c r="CO26" s="30">
         <v>0</v>
       </c>
-      <c r="CP26" s="97">
+      <c r="CP26" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A27" s="74" t="s">
+      <c r="A27" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="96">
+      <c r="B27" s="68">
         <v>1</v>
       </c>
       <c r="C27" s="15">
@@ -9434,15 +9427,15 @@
       <c r="CO27" s="30">
         <v>0</v>
       </c>
-      <c r="CP27" s="97">
+      <c r="CP27" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A28" s="74" t="s">
+      <c r="A28" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="96">
+      <c r="B28" s="68">
         <v>1</v>
       </c>
       <c r="C28" s="15">
@@ -9718,15 +9711,15 @@
       <c r="CO28" s="30">
         <v>0</v>
       </c>
-      <c r="CP28" s="97">
+      <c r="CP28" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A29" s="74" t="s">
+      <c r="A29" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="96">
+      <c r="B29" s="68">
         <v>1</v>
       </c>
       <c r="C29" s="15">
@@ -10002,15 +9995,15 @@
       <c r="CO29" s="30">
         <v>0</v>
       </c>
-      <c r="CP29" s="97">
+      <c r="CP29" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A30" s="74" t="s">
+      <c r="A30" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="96">
+      <c r="B30" s="68">
         <v>1</v>
       </c>
       <c r="C30" s="15">
@@ -10286,15 +10279,15 @@
       <c r="CO30" s="30">
         <v>0</v>
       </c>
-      <c r="CP30" s="97">
+      <c r="CP30" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A31" s="74" t="s">
+      <c r="A31" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="96">
+      <c r="B31" s="68">
         <v>1</v>
       </c>
       <c r="C31" s="15">
@@ -10570,15 +10563,15 @@
       <c r="CO31" s="30">
         <v>0</v>
       </c>
-      <c r="CP31" s="97">
+      <c r="CP31" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A32" s="74" t="s">
+      <c r="A32" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="96">
+      <c r="B32" s="68">
         <v>1</v>
       </c>
       <c r="C32" s="15">
@@ -10854,15 +10847,15 @@
       <c r="CO32" s="30">
         <v>0</v>
       </c>
-      <c r="CP32" s="97">
+      <c r="CP32" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A33" s="74" t="s">
+      <c r="A33" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="96">
+      <c r="B33" s="68">
         <v>1</v>
       </c>
       <c r="C33" s="15">
@@ -11138,15 +11131,15 @@
       <c r="CO33" s="30">
         <v>0</v>
       </c>
-      <c r="CP33" s="97">
+      <c r="CP33" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A34" s="74" t="s">
+      <c r="A34" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="96">
+      <c r="B34" s="68">
         <v>1</v>
       </c>
       <c r="C34" s="15">
@@ -11422,15 +11415,15 @@
       <c r="CO34" s="30">
         <v>0</v>
       </c>
-      <c r="CP34" s="97">
+      <c r="CP34" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A35" s="74" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="96">
+      <c r="A35" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="68">
         <v>1</v>
       </c>
       <c r="C35" s="15">
@@ -11706,15 +11699,15 @@
       <c r="CO35" s="30">
         <v>0</v>
       </c>
-      <c r="CP35" s="97">
+      <c r="CP35" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A36" s="74" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="96">
+      <c r="A36" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="68">
         <v>1</v>
       </c>
       <c r="C36" s="15">
@@ -11990,15 +11983,15 @@
       <c r="CO36" s="30">
         <v>0</v>
       </c>
-      <c r="CP36" s="97">
+      <c r="CP36" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A37" s="74" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="96">
+      <c r="A37" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="68">
         <v>1</v>
       </c>
       <c r="C37" s="15">
@@ -12274,15 +12267,15 @@
       <c r="CO37" s="30">
         <v>0</v>
       </c>
-      <c r="CP37" s="97">
+      <c r="CP37" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A38" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="96">
+      <c r="A38" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="68">
         <v>1</v>
       </c>
       <c r="C38" s="15">
@@ -12558,15 +12551,15 @@
       <c r="CO38" s="30">
         <v>0</v>
       </c>
-      <c r="CP38" s="97">
+      <c r="CP38" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:94" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A39" s="74" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="96">
+      <c r="A39" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="68">
         <v>1</v>
       </c>
       <c r="C39" s="15">
@@ -12842,15 +12835,15 @@
       <c r="CO39" s="30">
         <v>0</v>
       </c>
-      <c r="CP39" s="97">
+      <c r="CP39" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:94" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A40" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="96">
+      <c r="A40" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" s="68">
         <v>1</v>
       </c>
       <c r="C40" s="15">
@@ -13126,15 +13119,15 @@
       <c r="CO40" s="30">
         <v>0</v>
       </c>
-      <c r="CP40" s="97">
+      <c r="CP40" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:94" ht="14.25" x14ac:dyDescent="0.45">
-      <c r="A41" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" s="96">
+      <c r="A41" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="68">
         <v>1</v>
       </c>
       <c r="C41" s="15">
@@ -13410,1683 +13403,1683 @@
       <c r="CO41" s="30">
         <v>0</v>
       </c>
-      <c r="CP41" s="97">
+      <c r="CP41" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:94" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A42" s="77" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" s="98">
-        <v>1</v>
-      </c>
-      <c r="C42" s="99">
-        <v>0</v>
-      </c>
-      <c r="D42" s="99">
-        <v>0</v>
-      </c>
-      <c r="E42" s="99">
-        <v>0</v>
-      </c>
-      <c r="F42" s="99">
-        <v>0</v>
-      </c>
-      <c r="G42" s="99">
-        <v>0</v>
-      </c>
-      <c r="H42" s="99">
-        <v>0</v>
-      </c>
-      <c r="I42" s="99">
-        <v>0</v>
-      </c>
-      <c r="J42" s="99">
-        <v>0</v>
-      </c>
-      <c r="K42" s="99">
-        <v>0</v>
-      </c>
-      <c r="L42" s="99">
-        <v>0</v>
-      </c>
-      <c r="M42" s="99">
-        <v>0</v>
-      </c>
-      <c r="N42" s="99">
-        <v>0</v>
-      </c>
-      <c r="O42" s="99">
-        <v>0</v>
-      </c>
-      <c r="P42" s="99">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="99">
-        <v>0</v>
-      </c>
-      <c r="R42" s="99">
-        <v>0</v>
-      </c>
-      <c r="S42" s="99">
-        <v>0</v>
-      </c>
-      <c r="T42" s="99">
-        <v>0</v>
-      </c>
-      <c r="U42" s="99">
-        <v>0</v>
-      </c>
-      <c r="V42" s="99">
-        <v>0</v>
-      </c>
-      <c r="W42" s="99">
-        <v>0</v>
-      </c>
-      <c r="X42" s="99">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="99">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="100">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="100">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="100">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="100">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="100">
-        <v>1</v>
-      </c>
-      <c r="AE42" s="100">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="100">
-        <v>1</v>
-      </c>
-      <c r="AG42" s="101">
-        <v>1</v>
-      </c>
-      <c r="AH42" s="101">
-        <v>1</v>
-      </c>
-      <c r="AI42" s="101">
-        <v>1</v>
-      </c>
-      <c r="AJ42" s="101">
-        <v>1</v>
-      </c>
-      <c r="AK42" s="102">
-        <v>1</v>
-      </c>
-      <c r="AL42" s="102">
-        <v>1</v>
-      </c>
-      <c r="AM42" s="102">
-        <v>1</v>
-      </c>
-      <c r="AN42" s="102">
-        <v>1</v>
-      </c>
-      <c r="AO42" s="103">
-        <v>1</v>
-      </c>
-      <c r="AP42" s="103">
-        <v>1</v>
-      </c>
-      <c r="AQ42" s="103">
-        <v>1</v>
-      </c>
-      <c r="AR42" s="103">
-        <v>1</v>
-      </c>
-      <c r="AS42" s="104">
-        <v>1</v>
-      </c>
-      <c r="AT42" s="104">
-        <v>1</v>
-      </c>
-      <c r="AU42" s="104">
-        <v>1</v>
-      </c>
-      <c r="AV42" s="104">
-        <v>1</v>
-      </c>
-      <c r="AW42" s="105">
-        <v>1</v>
-      </c>
-      <c r="AX42" s="105">
-        <v>1</v>
-      </c>
-      <c r="AY42" s="105">
-        <v>1</v>
-      </c>
-      <c r="AZ42" s="105">
-        <v>1</v>
-      </c>
-      <c r="BA42" s="103">
-        <v>1</v>
-      </c>
-      <c r="BB42" s="103">
-        <v>1</v>
-      </c>
-      <c r="BC42" s="104">
-        <v>1</v>
-      </c>
-      <c r="BD42" s="104">
-        <v>1</v>
-      </c>
-      <c r="BE42" s="106">
-        <v>1</v>
-      </c>
-      <c r="BF42" s="106">
-        <v>1</v>
-      </c>
-      <c r="BG42" s="102">
-        <v>1</v>
-      </c>
-      <c r="BH42" s="102">
-        <v>1</v>
-      </c>
-      <c r="BI42" s="102">
-        <v>1</v>
-      </c>
-      <c r="BJ42" s="102">
-        <v>1</v>
-      </c>
-      <c r="BK42" s="107">
-        <v>1</v>
-      </c>
-      <c r="BL42" s="107">
-        <v>1</v>
-      </c>
-      <c r="BM42" s="107">
-        <v>1</v>
-      </c>
-      <c r="BN42" s="107">
-        <v>1</v>
-      </c>
-      <c r="BO42" s="107">
-        <v>1</v>
-      </c>
-      <c r="BP42" s="107">
-        <v>1</v>
-      </c>
-      <c r="BQ42" s="103">
-        <v>1</v>
-      </c>
-      <c r="BR42" s="103">
-        <v>1</v>
-      </c>
-      <c r="BS42" s="103">
-        <v>1</v>
-      </c>
-      <c r="BT42" s="103">
-        <v>1</v>
-      </c>
-      <c r="BU42" s="103">
-        <v>1</v>
-      </c>
-      <c r="BV42" s="103">
-        <v>1</v>
-      </c>
-      <c r="BW42" s="102">
-        <v>1</v>
-      </c>
-      <c r="BX42" s="102">
-        <v>1</v>
-      </c>
-      <c r="BY42" s="102">
-        <v>1</v>
-      </c>
-      <c r="BZ42" s="108">
-        <v>1</v>
-      </c>
-      <c r="CA42" s="108">
-        <v>1</v>
-      </c>
-      <c r="CB42" s="109">
-        <v>1</v>
-      </c>
-      <c r="CC42" s="109">
-        <v>1</v>
-      </c>
-      <c r="CD42" s="109">
-        <v>1</v>
-      </c>
-      <c r="CE42" s="109">
-        <v>1</v>
-      </c>
-      <c r="CF42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CG42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CH42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CI42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CJ42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CK42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CL42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CM42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CN42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CO42" s="110">
-        <v>0</v>
-      </c>
-      <c r="CP42" s="111">
+      <c r="A42" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="70">
+        <v>1</v>
+      </c>
+      <c r="C42" s="71">
+        <v>0</v>
+      </c>
+      <c r="D42" s="71">
+        <v>0</v>
+      </c>
+      <c r="E42" s="71">
+        <v>0</v>
+      </c>
+      <c r="F42" s="71">
+        <v>0</v>
+      </c>
+      <c r="G42" s="71">
+        <v>0</v>
+      </c>
+      <c r="H42" s="71">
+        <v>0</v>
+      </c>
+      <c r="I42" s="71">
+        <v>0</v>
+      </c>
+      <c r="J42" s="71">
+        <v>0</v>
+      </c>
+      <c r="K42" s="71">
+        <v>0</v>
+      </c>
+      <c r="L42" s="71">
+        <v>0</v>
+      </c>
+      <c r="M42" s="71">
+        <v>0</v>
+      </c>
+      <c r="N42" s="71">
+        <v>0</v>
+      </c>
+      <c r="O42" s="71">
+        <v>0</v>
+      </c>
+      <c r="P42" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="71">
+        <v>0</v>
+      </c>
+      <c r="R42" s="71">
+        <v>0</v>
+      </c>
+      <c r="S42" s="71">
+        <v>0</v>
+      </c>
+      <c r="T42" s="71">
+        <v>0</v>
+      </c>
+      <c r="U42" s="71">
+        <v>0</v>
+      </c>
+      <c r="V42" s="71">
+        <v>0</v>
+      </c>
+      <c r="W42" s="71">
+        <v>0</v>
+      </c>
+      <c r="X42" s="71">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="71">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="72">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="72">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="72">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="72">
+        <v>1</v>
+      </c>
+      <c r="AD42" s="72">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="72">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="72">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="73">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="73">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="73">
+        <v>1</v>
+      </c>
+      <c r="AJ42" s="73">
+        <v>1</v>
+      </c>
+      <c r="AK42" s="74">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="74">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="74">
+        <v>1</v>
+      </c>
+      <c r="AN42" s="74">
+        <v>1</v>
+      </c>
+      <c r="AO42" s="75">
+        <v>1</v>
+      </c>
+      <c r="AP42" s="75">
+        <v>1</v>
+      </c>
+      <c r="AQ42" s="75">
+        <v>1</v>
+      </c>
+      <c r="AR42" s="75">
+        <v>1</v>
+      </c>
+      <c r="AS42" s="76">
+        <v>1</v>
+      </c>
+      <c r="AT42" s="76">
+        <v>1</v>
+      </c>
+      <c r="AU42" s="76">
+        <v>1</v>
+      </c>
+      <c r="AV42" s="76">
+        <v>1</v>
+      </c>
+      <c r="AW42" s="77">
+        <v>1</v>
+      </c>
+      <c r="AX42" s="77">
+        <v>1</v>
+      </c>
+      <c r="AY42" s="77">
+        <v>1</v>
+      </c>
+      <c r="AZ42" s="77">
+        <v>1</v>
+      </c>
+      <c r="BA42" s="75">
+        <v>1</v>
+      </c>
+      <c r="BB42" s="75">
+        <v>1</v>
+      </c>
+      <c r="BC42" s="76">
+        <v>1</v>
+      </c>
+      <c r="BD42" s="76">
+        <v>1</v>
+      </c>
+      <c r="BE42" s="78">
+        <v>1</v>
+      </c>
+      <c r="BF42" s="78">
+        <v>1</v>
+      </c>
+      <c r="BG42" s="74">
+        <v>1</v>
+      </c>
+      <c r="BH42" s="74">
+        <v>1</v>
+      </c>
+      <c r="BI42" s="74">
+        <v>1</v>
+      </c>
+      <c r="BJ42" s="74">
+        <v>1</v>
+      </c>
+      <c r="BK42" s="79">
+        <v>1</v>
+      </c>
+      <c r="BL42" s="79">
+        <v>1</v>
+      </c>
+      <c r="BM42" s="79">
+        <v>1</v>
+      </c>
+      <c r="BN42" s="79">
+        <v>1</v>
+      </c>
+      <c r="BO42" s="79">
+        <v>1</v>
+      </c>
+      <c r="BP42" s="79">
+        <v>1</v>
+      </c>
+      <c r="BQ42" s="75">
+        <v>1</v>
+      </c>
+      <c r="BR42" s="75">
+        <v>1</v>
+      </c>
+      <c r="BS42" s="75">
+        <v>1</v>
+      </c>
+      <c r="BT42" s="75">
+        <v>1</v>
+      </c>
+      <c r="BU42" s="75">
+        <v>1</v>
+      </c>
+      <c r="BV42" s="75">
+        <v>1</v>
+      </c>
+      <c r="BW42" s="74">
+        <v>1</v>
+      </c>
+      <c r="BX42" s="74">
+        <v>1</v>
+      </c>
+      <c r="BY42" s="74">
+        <v>1</v>
+      </c>
+      <c r="BZ42" s="80">
+        <v>1</v>
+      </c>
+      <c r="CA42" s="80">
+        <v>1</v>
+      </c>
+      <c r="CB42" s="81">
+        <v>1</v>
+      </c>
+      <c r="CC42" s="81">
+        <v>1</v>
+      </c>
+      <c r="CD42" s="81">
+        <v>1</v>
+      </c>
+      <c r="CE42" s="81">
+        <v>1</v>
+      </c>
+      <c r="CF42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CG42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CH42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CI42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CJ42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CK42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CL42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CM42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CN42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CO42" s="82">
+        <v>0</v>
+      </c>
+      <c r="CP42" s="83">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:94" ht="14.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A43" s="67" t="s">
-        <v>93</v>
+    <row r="43" spans="1:94" x14ac:dyDescent="0.45">
+      <c r="A43" s="115" t="s">
+        <v>92</v>
       </c>
       <c r="B43" s="112">
         <f>SUM(B8:B21)</f>
         <v>70</v>
       </c>
-      <c r="C43" s="113">
+      <c r="C43" s="84">
         <f t="shared" ref="C43:BN43" si="0">SUM(C8:C21)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="113">
+      <c r="D43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E43" s="113">
+      <c r="E43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F43" s="113">
+      <c r="F43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G43" s="113">
+      <c r="G43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H43" s="113">
+      <c r="H43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I43" s="113">
+      <c r="I43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J43" s="113">
+      <c r="J43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K43" s="113">
+      <c r="K43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L43" s="113">
+      <c r="L43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M43" s="113">
+      <c r="M43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N43" s="113">
+      <c r="N43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O43" s="113">
+      <c r="O43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P43" s="113">
+      <c r="P43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q43" s="113">
+      <c r="Q43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R43" s="113">
+      <c r="R43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S43" s="113">
+      <c r="S43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T43" s="113">
+      <c r="T43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U43" s="113">
+      <c r="U43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V43" s="113">
+      <c r="V43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W43" s="113">
+      <c r="W43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X43" s="113">
+      <c r="X43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y43" s="113">
+      <c r="Y43" s="84">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Z43" s="113">
+      <c r="Z43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AA43" s="113">
+      <c r="AA43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AB43" s="113">
+      <c r="AB43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AC43" s="113">
+      <c r="AC43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AD43" s="113">
+      <c r="AD43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AE43" s="113">
+      <c r="AE43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AF43" s="113">
+      <c r="AF43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AG43" s="113">
+      <c r="AG43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AH43" s="113">
+      <c r="AH43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AI43" s="113">
+      <c r="AI43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AJ43" s="113">
+      <c r="AJ43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AK43" s="113">
+      <c r="AK43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AL43" s="113">
+      <c r="AL43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AM43" s="113">
+      <c r="AM43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AN43" s="113">
+      <c r="AN43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AO43" s="113">
+      <c r="AO43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AP43" s="113">
+      <c r="AP43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AQ43" s="113">
+      <c r="AQ43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AR43" s="113">
+      <c r="AR43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AS43" s="113">
+      <c r="AS43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AT43" s="113">
+      <c r="AT43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AU43" s="113">
+      <c r="AU43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AV43" s="113">
+      <c r="AV43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AW43" s="113">
+      <c r="AW43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AX43" s="113">
+      <c r="AX43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AY43" s="113">
+      <c r="AY43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="AZ43" s="113">
+      <c r="AZ43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BA43" s="113">
+      <c r="BA43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BB43" s="113">
+      <c r="BB43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BC43" s="113">
+      <c r="BC43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BD43" s="113">
+      <c r="BD43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BE43" s="113">
+      <c r="BE43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BF43" s="113">
+      <c r="BF43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BG43" s="113">
+      <c r="BG43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BH43" s="113">
+      <c r="BH43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BI43" s="113">
+      <c r="BI43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BJ43" s="113">
+      <c r="BJ43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BK43" s="113">
+      <c r="BK43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BL43" s="113">
+      <c r="BL43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BM43" s="113">
+      <c r="BM43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BN43" s="113">
+      <c r="BN43" s="84">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="BO43" s="113">
+      <c r="BO43" s="84">
         <f t="shared" ref="BO43:CP43" si="1">SUM(BO8:BO21)</f>
         <v>70</v>
       </c>
-      <c r="BP43" s="113">
+      <c r="BP43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BQ43" s="113">
+      <c r="BQ43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BR43" s="113">
+      <c r="BR43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BS43" s="113">
+      <c r="BS43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BT43" s="113">
+      <c r="BT43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BU43" s="113">
+      <c r="BU43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BV43" s="113">
+      <c r="BV43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BW43" s="113">
+      <c r="BW43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BX43" s="113">
+      <c r="BX43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BY43" s="113">
+      <c r="BY43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="BZ43" s="113">
+      <c r="BZ43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="CA43" s="113">
+      <c r="CA43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="CB43" s="113">
+      <c r="CB43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="CC43" s="113">
+      <c r="CC43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="CD43" s="113">
+      <c r="CD43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="CE43" s="113">
+      <c r="CE43" s="84">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="CF43" s="113">
+      <c r="CF43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CG43" s="113">
+      <c r="CG43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CH43" s="113">
+      <c r="CH43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CI43" s="113">
+      <c r="CI43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CJ43" s="113">
+      <c r="CJ43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CK43" s="113">
+      <c r="CK43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CL43" s="113">
+      <c r="CL43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CM43" s="113">
+      <c r="CM43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CN43" s="113">
+      <c r="CN43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CO43" s="113">
+      <c r="CO43" s="84">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="CP43" s="114">
+      <c r="CP43" s="85">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:94" ht="14.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A44" s="68" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="69">
+    <row r="44" spans="1:94" x14ac:dyDescent="0.45">
+      <c r="A44" s="116" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" s="113">
         <f>SUM(B4:B7, B22:B42)</f>
         <v>54</v>
       </c>
-      <c r="C44" s="65">
+      <c r="C44" s="41">
         <f t="shared" ref="C44:BN44" si="2">SUM(C4:C7, C22:C42)</f>
         <v>0</v>
       </c>
-      <c r="D44" s="65">
+      <c r="D44" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E44" s="65">
+      <c r="E44" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F44" s="65">
+      <c r="F44" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G44" s="65">
+      <c r="G44" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H44" s="65">
+      <c r="H44" s="41">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I44" s="65">
+      <c r="I44" s="41">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="J44" s="65">
+      <c r="J44" s="41">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K44" s="65">
+      <c r="K44" s="41">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="L44" s="65">
+      <c r="L44" s="41">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="M44" s="65">
+      <c r="M44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="N44" s="65">
+      <c r="N44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="O44" s="65">
+      <c r="O44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="P44" s="65">
+      <c r="P44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="Q44" s="65">
+      <c r="Q44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="R44" s="65">
+      <c r="R44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="S44" s="65">
+      <c r="S44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="T44" s="65">
+      <c r="T44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="U44" s="65">
+      <c r="U44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="V44" s="65">
+      <c r="V44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="W44" s="65">
+      <c r="W44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="X44" s="65">
+      <c r="X44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="Y44" s="65">
+      <c r="Y44" s="41">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="Z44" s="65">
+      <c r="Z44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AA44" s="65">
+      <c r="AA44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AB44" s="65">
+      <c r="AB44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AC44" s="65">
+      <c r="AC44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AD44" s="65">
+      <c r="AD44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AE44" s="65">
+      <c r="AE44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AF44" s="65">
+      <c r="AF44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AG44" s="65">
+      <c r="AG44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AH44" s="65">
+      <c r="AH44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AI44" s="65">
+      <c r="AI44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AJ44" s="65">
+      <c r="AJ44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AK44" s="65">
+      <c r="AK44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AL44" s="65">
+      <c r="AL44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AM44" s="65">
+      <c r="AM44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AN44" s="65">
+      <c r="AN44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AO44" s="65">
+      <c r="AO44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AP44" s="65">
+      <c r="AP44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AQ44" s="65">
+      <c r="AQ44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AR44" s="65">
+      <c r="AR44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AS44" s="65">
+      <c r="AS44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AT44" s="65">
+      <c r="AT44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AU44" s="65">
+      <c r="AU44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AV44" s="65">
+      <c r="AV44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="AW44" s="65">
+      <c r="AW44" s="41">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="AX44" s="65">
+      <c r="AX44" s="41">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="AY44" s="65">
+      <c r="AY44" s="41">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="AZ44" s="65">
+      <c r="AZ44" s="41">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="BA44" s="65">
+      <c r="BA44" s="41">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="BB44" s="65">
+      <c r="BB44" s="41">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="BC44" s="65">
+      <c r="BC44" s="41">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="BD44" s="65">
+      <c r="BD44" s="41">
         <f t="shared" si="2"/>
         <v>49</v>
       </c>
-      <c r="BE44" s="65">
+      <c r="BE44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BF44" s="65">
+      <c r="BF44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BG44" s="65">
+      <c r="BG44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BH44" s="65">
+      <c r="BH44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BI44" s="65">
+      <c r="BI44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BJ44" s="65">
+      <c r="BJ44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BK44" s="65">
+      <c r="BK44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BL44" s="65">
+      <c r="BL44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BM44" s="65">
+      <c r="BM44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BN44" s="65">
+      <c r="BN44" s="41">
         <f t="shared" si="2"/>
         <v>54</v>
       </c>
-      <c r="BO44" s="65">
+      <c r="BO44" s="41">
         <f t="shared" ref="BO44:CP44" si="3">SUM(BO4:BO7, BO22:BO42)</f>
         <v>54</v>
       </c>
-      <c r="BP44" s="65">
+      <c r="BP44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BQ44" s="65">
+      <c r="BQ44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BR44" s="65">
+      <c r="BR44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BS44" s="65">
+      <c r="BS44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BT44" s="65">
+      <c r="BT44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BU44" s="65">
+      <c r="BU44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BV44" s="65">
+      <c r="BV44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BW44" s="65">
+      <c r="BW44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BX44" s="65">
+      <c r="BX44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BY44" s="65">
+      <c r="BY44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="BZ44" s="65">
+      <c r="BZ44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="CA44" s="65">
+      <c r="CA44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="CB44" s="65">
+      <c r="CB44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="CC44" s="65">
+      <c r="CC44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="CD44" s="65">
+      <c r="CD44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="CE44" s="65">
+      <c r="CE44" s="41">
         <f t="shared" si="3"/>
         <v>54</v>
       </c>
-      <c r="CF44" s="65">
+      <c r="CF44" s="41">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="CG44" s="65">
+      <c r="CG44" s="41">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="CH44" s="65">
+      <c r="CH44" s="41">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="CI44" s="65">
+      <c r="CI44" s="41">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="CJ44" s="65">
+      <c r="CJ44" s="41">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="CK44" s="65">
+      <c r="CK44" s="41">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="CL44" s="65">
+      <c r="CL44" s="41">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CM44" s="65">
+      <c r="CM44" s="41">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CN44" s="65">
+      <c r="CN44" s="41">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="CO44" s="65">
+      <c r="CO44" s="41">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="CP44" s="70">
+      <c r="CP44" s="43">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:94" ht="14.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A45" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="B45" s="71">
+      <c r="A45" s="117" t="s">
+        <v>71</v>
+      </c>
+      <c r="B45" s="114">
         <f>SUM(B4:B42)</f>
         <v>124</v>
       </c>
-      <c r="C45" s="66">
+      <c r="C45" s="42">
         <f t="shared" ref="C45:BN45" si="4">SUM(C4:C42)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="66">
+      <c r="D45" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="E45" s="66">
+      <c r="E45" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F45" s="66">
+      <c r="F45" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G45" s="66">
+      <c r="G45" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H45" s="66">
+      <c r="H45" s="42">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I45" s="66">
+      <c r="I45" s="42">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="J45" s="66">
+      <c r="J45" s="42">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="K45" s="66">
+      <c r="K45" s="42">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="L45" s="66">
+      <c r="L45" s="42">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="M45" s="66">
+      <c r="M45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="N45" s="66">
+      <c r="N45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="O45" s="66">
+      <c r="O45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="P45" s="66">
+      <c r="P45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="Q45" s="66">
+      <c r="Q45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="R45" s="66">
+      <c r="R45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="S45" s="66">
+      <c r="S45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="T45" s="66">
+      <c r="T45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="U45" s="66">
+      <c r="U45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="V45" s="66">
+      <c r="V45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="W45" s="66">
+      <c r="W45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="X45" s="66">
+      <c r="X45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="Y45" s="66">
+      <c r="Y45" s="42">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="Z45" s="66">
+      <c r="Z45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AA45" s="66">
+      <c r="AA45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AB45" s="66">
+      <c r="AB45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AC45" s="66">
+      <c r="AC45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AD45" s="66">
+      <c r="AD45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AE45" s="66">
+      <c r="AE45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AF45" s="66">
+      <c r="AF45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AG45" s="66">
+      <c r="AG45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AH45" s="66">
+      <c r="AH45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AI45" s="66">
+      <c r="AI45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AJ45" s="66">
+      <c r="AJ45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AK45" s="66">
+      <c r="AK45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AL45" s="66">
+      <c r="AL45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AM45" s="66">
+      <c r="AM45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AN45" s="66">
+      <c r="AN45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AO45" s="66">
+      <c r="AO45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AP45" s="66">
+      <c r="AP45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AQ45" s="66">
+      <c r="AQ45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AR45" s="66">
+      <c r="AR45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AS45" s="66">
+      <c r="AS45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AT45" s="66">
+      <c r="AT45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AU45" s="66">
+      <c r="AU45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AV45" s="66">
+      <c r="AV45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="AW45" s="66">
+      <c r="AW45" s="42">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="AX45" s="66">
+      <c r="AX45" s="42">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="AY45" s="66">
+      <c r="AY45" s="42">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="AZ45" s="66">
+      <c r="AZ45" s="42">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="BA45" s="66">
+      <c r="BA45" s="42">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="BB45" s="66">
+      <c r="BB45" s="42">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="BC45" s="66">
+      <c r="BC45" s="42">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="BD45" s="66">
+      <c r="BD45" s="42">
         <f t="shared" si="4"/>
         <v>119</v>
       </c>
-      <c r="BE45" s="66">
+      <c r="BE45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BF45" s="66">
+      <c r="BF45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BG45" s="66">
+      <c r="BG45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BH45" s="66">
+      <c r="BH45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BI45" s="66">
+      <c r="BI45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BJ45" s="66">
+      <c r="BJ45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BK45" s="66">
+      <c r="BK45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BL45" s="66">
+      <c r="BL45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BM45" s="66">
+      <c r="BM45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BN45" s="66">
+      <c r="BN45" s="42">
         <f t="shared" si="4"/>
         <v>124</v>
       </c>
-      <c r="BO45" s="66">
+      <c r="BO45" s="42">
         <f t="shared" ref="BO45:CP45" si="5">SUM(BO4:BO42)</f>
         <v>124</v>
       </c>
-      <c r="BP45" s="66">
+      <c r="BP45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BQ45" s="66">
+      <c r="BQ45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BR45" s="66">
+      <c r="BR45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BS45" s="66">
+      <c r="BS45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BT45" s="66">
+      <c r="BT45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BU45" s="66">
+      <c r="BU45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BV45" s="66">
+      <c r="BV45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BW45" s="66">
+      <c r="BW45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BX45" s="66">
+      <c r="BX45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BY45" s="66">
+      <c r="BY45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="BZ45" s="66">
+      <c r="BZ45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="CA45" s="66">
+      <c r="CA45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="CB45" s="66">
+      <c r="CB45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="CC45" s="66">
+      <c r="CC45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="CD45" s="66">
+      <c r="CD45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="CE45" s="66">
+      <c r="CE45" s="42">
         <f t="shared" si="5"/>
         <v>124</v>
       </c>
-      <c r="CF45" s="66">
+      <c r="CF45" s="42">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CG45" s="66">
+      <c r="CG45" s="42">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CH45" s="66">
+      <c r="CH45" s="42">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CI45" s="66">
+      <c r="CI45" s="42">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CJ45" s="66">
+      <c r="CJ45" s="42">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CK45" s="66">
+      <c r="CK45" s="42">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="CL45" s="66">
+      <c r="CL45" s="42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CM45" s="66">
+      <c r="CM45" s="42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CN45" s="66">
+      <c r="CN45" s="42">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
-      <c r="CO45" s="66">
+      <c r="CO45" s="42">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="CP45" s="72">
+      <c r="CP45" s="44">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:94" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="63" t="s">
+      <c r="A46" s="98" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="E46" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="B46" s="16"/>
-      <c r="E46" s="48" t="s">
+      <c r="I46" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="I46" s="48" t="s">
+      <c r="K46" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="K46" s="48" t="s">
+      <c r="O46" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="O46" s="48" t="s">
+      <c r="W46" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="W46" s="48" t="s">
+      <c r="AM46" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="AM46" s="48" t="s">
+      <c r="AO46" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="AO46" s="58" t="s">
+      <c r="AS46" s="94" t="s">
         <v>86</v>
       </c>
-      <c r="AS46" s="48" t="s">
+      <c r="AU46" s="94" t="s">
         <v>87</v>
       </c>
-      <c r="AU46" s="48" t="s">
+      <c r="AW46" s="92" t="s">
         <v>88</v>
       </c>
-      <c r="AW46" s="56" t="s">
+      <c r="AX46" s="92" t="s">
         <v>89</v>
       </c>
-      <c r="AX46" s="56" t="s">
+      <c r="BK46" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="BK46" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="BL46" s="64"/>
-      <c r="BM46" s="64"/>
-      <c r="BN46" s="64"/>
-      <c r="BO46" s="64"/>
-      <c r="BP46" s="64"/>
-      <c r="BQ46" s="64"/>
-      <c r="BR46" s="64"/>
-      <c r="BS46" s="64"/>
-      <c r="BT46" s="64"/>
-      <c r="BU46" s="64"/>
-      <c r="BV46" s="64"/>
-      <c r="BW46" s="64"/>
-      <c r="BX46" s="64"/>
-      <c r="BY46" s="64"/>
-      <c r="BZ46" s="64"/>
-      <c r="CA46" s="64"/>
-      <c r="CB46" s="64"/>
-      <c r="CC46" s="64"/>
-      <c r="CD46" s="64"/>
-      <c r="CE46" s="64"/>
-      <c r="CF46" s="64"/>
-      <c r="CG46" s="64"/>
-      <c r="CH46" s="64"/>
-      <c r="CI46" s="64"/>
-      <c r="CJ46" s="64"/>
-      <c r="CK46" s="64"/>
-      <c r="CL46" s="64"/>
-      <c r="CM46" s="64"/>
-      <c r="CN46" s="52"/>
+      <c r="BL46" s="87"/>
+      <c r="BM46" s="87"/>
+      <c r="BN46" s="87"/>
+      <c r="BO46" s="87"/>
+      <c r="BP46" s="87"/>
+      <c r="BQ46" s="87"/>
+      <c r="BR46" s="87"/>
+      <c r="BS46" s="87"/>
+      <c r="BT46" s="87"/>
+      <c r="BU46" s="87"/>
+      <c r="BV46" s="87"/>
+      <c r="BW46" s="87"/>
+      <c r="BX46" s="87"/>
+      <c r="BY46" s="87"/>
+      <c r="BZ46" s="87"/>
+      <c r="CA46" s="87"/>
+      <c r="CB46" s="87"/>
+      <c r="CC46" s="87"/>
+      <c r="CD46" s="87"/>
+      <c r="CE46" s="87"/>
+      <c r="CF46" s="87"/>
+      <c r="CG46" s="87"/>
+      <c r="CH46" s="87"/>
+      <c r="CI46" s="87"/>
+      <c r="CJ46" s="87"/>
+      <c r="CK46" s="87"/>
+      <c r="CL46" s="87"/>
+      <c r="CM46" s="87"/>
+      <c r="CN46" s="88"/>
     </row>
     <row r="47" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A47" s="60"/>
+      <c r="A47" s="99"/>
       <c r="B47" s="16"/>
-      <c r="E47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="K47" s="48"/>
-      <c r="O47" s="48"/>
-      <c r="W47" s="48"/>
-      <c r="AM47" s="48"/>
-      <c r="AO47" s="58"/>
-      <c r="AS47" s="48"/>
-      <c r="AU47" s="48"/>
-      <c r="AW47" s="56"/>
-      <c r="AX47" s="56"/>
-      <c r="BK47" s="50"/>
-      <c r="BL47" s="51"/>
-      <c r="BM47" s="51"/>
-      <c r="BN47" s="51"/>
-      <c r="BO47" s="51"/>
-      <c r="BP47" s="51"/>
-      <c r="BQ47" s="51"/>
-      <c r="BR47" s="51"/>
-      <c r="BS47" s="51"/>
-      <c r="BT47" s="51"/>
-      <c r="BU47" s="51"/>
-      <c r="BV47" s="51"/>
-      <c r="BW47" s="51"/>
-      <c r="BX47" s="51"/>
-      <c r="BY47" s="51"/>
-      <c r="BZ47" s="51"/>
-      <c r="CA47" s="51"/>
-      <c r="CB47" s="51"/>
-      <c r="CC47" s="51"/>
-      <c r="CD47" s="51"/>
-      <c r="CE47" s="51"/>
-      <c r="CF47" s="51"/>
-      <c r="CG47" s="51"/>
-      <c r="CH47" s="51"/>
-      <c r="CI47" s="51"/>
-      <c r="CJ47" s="51"/>
-      <c r="CK47" s="51"/>
-      <c r="CL47" s="51"/>
-      <c r="CM47" s="51"/>
-      <c r="CN47" s="52"/>
+      <c r="E47" s="94"/>
+      <c r="I47" s="94"/>
+      <c r="K47" s="94"/>
+      <c r="O47" s="94"/>
+      <c r="W47" s="94"/>
+      <c r="AM47" s="94"/>
+      <c r="AO47" s="96"/>
+      <c r="AS47" s="94"/>
+      <c r="AU47" s="94"/>
+      <c r="AW47" s="92"/>
+      <c r="AX47" s="92"/>
+      <c r="BK47" s="86"/>
+      <c r="BL47" s="87"/>
+      <c r="BM47" s="87"/>
+      <c r="BN47" s="87"/>
+      <c r="BO47" s="87"/>
+      <c r="BP47" s="87"/>
+      <c r="BQ47" s="87"/>
+      <c r="BR47" s="87"/>
+      <c r="BS47" s="87"/>
+      <c r="BT47" s="87"/>
+      <c r="BU47" s="87"/>
+      <c r="BV47" s="87"/>
+      <c r="BW47" s="87"/>
+      <c r="BX47" s="87"/>
+      <c r="BY47" s="87"/>
+      <c r="BZ47" s="87"/>
+      <c r="CA47" s="87"/>
+      <c r="CB47" s="87"/>
+      <c r="CC47" s="87"/>
+      <c r="CD47" s="87"/>
+      <c r="CE47" s="87"/>
+      <c r="CF47" s="87"/>
+      <c r="CG47" s="87"/>
+      <c r="CH47" s="87"/>
+      <c r="CI47" s="87"/>
+      <c r="CJ47" s="87"/>
+      <c r="CK47" s="87"/>
+      <c r="CL47" s="87"/>
+      <c r="CM47" s="87"/>
+      <c r="CN47" s="88"/>
     </row>
     <row r="48" spans="1:94" x14ac:dyDescent="0.45">
-      <c r="A48" s="60"/>
+      <c r="A48" s="99"/>
       <c r="B48" s="16"/>
-      <c r="E48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="K48" s="48"/>
-      <c r="O48" s="48"/>
-      <c r="W48" s="48"/>
-      <c r="AM48" s="48"/>
-      <c r="AO48" s="58"/>
-      <c r="AS48" s="48"/>
-      <c r="AU48" s="48"/>
-      <c r="AW48" s="56"/>
-      <c r="AX48" s="56"/>
-      <c r="BK48" s="50"/>
-      <c r="BL48" s="51"/>
-      <c r="BM48" s="51"/>
-      <c r="BN48" s="51"/>
-      <c r="BO48" s="51"/>
-      <c r="BP48" s="51"/>
-      <c r="BQ48" s="51"/>
-      <c r="BR48" s="51"/>
-      <c r="BS48" s="51"/>
-      <c r="BT48" s="51"/>
-      <c r="BU48" s="51"/>
-      <c r="BV48" s="51"/>
-      <c r="BW48" s="51"/>
-      <c r="BX48" s="51"/>
-      <c r="BY48" s="51"/>
-      <c r="BZ48" s="51"/>
-      <c r="CA48" s="51"/>
-      <c r="CB48" s="51"/>
-      <c r="CC48" s="51"/>
-      <c r="CD48" s="51"/>
-      <c r="CE48" s="51"/>
-      <c r="CF48" s="51"/>
-      <c r="CG48" s="51"/>
-      <c r="CH48" s="51"/>
-      <c r="CI48" s="51"/>
-      <c r="CJ48" s="51"/>
-      <c r="CK48" s="51"/>
-      <c r="CL48" s="51"/>
-      <c r="CM48" s="51"/>
-      <c r="CN48" s="52"/>
+      <c r="E48" s="94"/>
+      <c r="I48" s="94"/>
+      <c r="K48" s="94"/>
+      <c r="O48" s="94"/>
+      <c r="W48" s="94"/>
+      <c r="AM48" s="94"/>
+      <c r="AO48" s="96"/>
+      <c r="AS48" s="94"/>
+      <c r="AU48" s="94"/>
+      <c r="AW48" s="92"/>
+      <c r="AX48" s="92"/>
+      <c r="BK48" s="86"/>
+      <c r="BL48" s="87"/>
+      <c r="BM48" s="87"/>
+      <c r="BN48" s="87"/>
+      <c r="BO48" s="87"/>
+      <c r="BP48" s="87"/>
+      <c r="BQ48" s="87"/>
+      <c r="BR48" s="87"/>
+      <c r="BS48" s="87"/>
+      <c r="BT48" s="87"/>
+      <c r="BU48" s="87"/>
+      <c r="BV48" s="87"/>
+      <c r="BW48" s="87"/>
+      <c r="BX48" s="87"/>
+      <c r="BY48" s="87"/>
+      <c r="BZ48" s="87"/>
+      <c r="CA48" s="87"/>
+      <c r="CB48" s="87"/>
+      <c r="CC48" s="87"/>
+      <c r="CD48" s="87"/>
+      <c r="CE48" s="87"/>
+      <c r="CF48" s="87"/>
+      <c r="CG48" s="87"/>
+      <c r="CH48" s="87"/>
+      <c r="CI48" s="87"/>
+      <c r="CJ48" s="87"/>
+      <c r="CK48" s="87"/>
+      <c r="CL48" s="87"/>
+      <c r="CM48" s="87"/>
+      <c r="CN48" s="88"/>
     </row>
     <row r="49" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A49" s="60"/>
+      <c r="A49" s="99"/>
       <c r="B49" s="16"/>
-      <c r="E49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="K49" s="48"/>
-      <c r="O49" s="48"/>
-      <c r="W49" s="48"/>
-      <c r="AM49" s="48"/>
-      <c r="AO49" s="58"/>
-      <c r="AS49" s="48"/>
-      <c r="AU49" s="48"/>
-      <c r="AW49" s="56"/>
-      <c r="AX49" s="56"/>
-      <c r="BK49" s="50"/>
-      <c r="BL49" s="51"/>
-      <c r="BM49" s="51"/>
-      <c r="BN49" s="51"/>
-      <c r="BO49" s="51"/>
-      <c r="BP49" s="51"/>
-      <c r="BQ49" s="51"/>
-      <c r="BR49" s="51"/>
-      <c r="BS49" s="51"/>
-      <c r="BT49" s="51"/>
-      <c r="BU49" s="51"/>
-      <c r="BV49" s="51"/>
-      <c r="BW49" s="51"/>
-      <c r="BX49" s="51"/>
-      <c r="BY49" s="51"/>
-      <c r="BZ49" s="51"/>
-      <c r="CA49" s="51"/>
-      <c r="CB49" s="51"/>
-      <c r="CC49" s="51"/>
-      <c r="CD49" s="51"/>
-      <c r="CE49" s="51"/>
-      <c r="CF49" s="51"/>
-      <c r="CG49" s="51"/>
-      <c r="CH49" s="51"/>
-      <c r="CI49" s="51"/>
-      <c r="CJ49" s="51"/>
-      <c r="CK49" s="51"/>
-      <c r="CL49" s="51"/>
-      <c r="CM49" s="51"/>
-      <c r="CN49" s="52"/>
+      <c r="E49" s="94"/>
+      <c r="I49" s="94"/>
+      <c r="K49" s="94"/>
+      <c r="O49" s="94"/>
+      <c r="W49" s="94"/>
+      <c r="AM49" s="94"/>
+      <c r="AO49" s="96"/>
+      <c r="AS49" s="94"/>
+      <c r="AU49" s="94"/>
+      <c r="AW49" s="92"/>
+      <c r="AX49" s="92"/>
+      <c r="BK49" s="86"/>
+      <c r="BL49" s="87"/>
+      <c r="BM49" s="87"/>
+      <c r="BN49" s="87"/>
+      <c r="BO49" s="87"/>
+      <c r="BP49" s="87"/>
+      <c r="BQ49" s="87"/>
+      <c r="BR49" s="87"/>
+      <c r="BS49" s="87"/>
+      <c r="BT49" s="87"/>
+      <c r="BU49" s="87"/>
+      <c r="BV49" s="87"/>
+      <c r="BW49" s="87"/>
+      <c r="BX49" s="87"/>
+      <c r="BY49" s="87"/>
+      <c r="BZ49" s="87"/>
+      <c r="CA49" s="87"/>
+      <c r="CB49" s="87"/>
+      <c r="CC49" s="87"/>
+      <c r="CD49" s="87"/>
+      <c r="CE49" s="87"/>
+      <c r="CF49" s="87"/>
+      <c r="CG49" s="87"/>
+      <c r="CH49" s="87"/>
+      <c r="CI49" s="87"/>
+      <c r="CJ49" s="87"/>
+      <c r="CK49" s="87"/>
+      <c r="CL49" s="87"/>
+      <c r="CM49" s="87"/>
+      <c r="CN49" s="88"/>
     </row>
     <row r="50" spans="1:92" ht="14.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A50" s="61"/>
-      <c r="E50" s="49"/>
-      <c r="I50" s="49"/>
-      <c r="K50" s="49"/>
-      <c r="O50" s="49"/>
-      <c r="W50" s="49"/>
-      <c r="AM50" s="49"/>
-      <c r="AO50" s="59"/>
-      <c r="AS50" s="49"/>
-      <c r="AU50" s="49"/>
-      <c r="AW50" s="57"/>
-      <c r="AX50" s="57"/>
-      <c r="BK50" s="53"/>
-      <c r="BL50" s="54"/>
-      <c r="BM50" s="54"/>
-      <c r="BN50" s="54"/>
-      <c r="BO50" s="54"/>
-      <c r="BP50" s="54"/>
-      <c r="BQ50" s="54"/>
-      <c r="BR50" s="54"/>
-      <c r="BS50" s="54"/>
-      <c r="BT50" s="54"/>
-      <c r="BU50" s="54"/>
-      <c r="BV50" s="54"/>
-      <c r="BW50" s="54"/>
-      <c r="BX50" s="54"/>
-      <c r="BY50" s="54"/>
-      <c r="BZ50" s="54"/>
-      <c r="CA50" s="54"/>
-      <c r="CB50" s="54"/>
-      <c r="CC50" s="54"/>
-      <c r="CD50" s="54"/>
-      <c r="CE50" s="54"/>
-      <c r="CF50" s="54"/>
-      <c r="CG50" s="54"/>
-      <c r="CH50" s="54"/>
-      <c r="CI50" s="54"/>
-      <c r="CJ50" s="54"/>
-      <c r="CK50" s="54"/>
-      <c r="CL50" s="54"/>
-      <c r="CM50" s="54"/>
-      <c r="CN50" s="55"/>
+      <c r="A50" s="100"/>
+      <c r="E50" s="95"/>
+      <c r="I50" s="95"/>
+      <c r="K50" s="95"/>
+      <c r="O50" s="95"/>
+      <c r="W50" s="95"/>
+      <c r="AM50" s="95"/>
+      <c r="AO50" s="97"/>
+      <c r="AS50" s="95"/>
+      <c r="AU50" s="95"/>
+      <c r="AW50" s="93"/>
+      <c r="AX50" s="93"/>
+      <c r="BK50" s="89"/>
+      <c r="BL50" s="90"/>
+      <c r="BM50" s="90"/>
+      <c r="BN50" s="90"/>
+      <c r="BO50" s="90"/>
+      <c r="BP50" s="90"/>
+      <c r="BQ50" s="90"/>
+      <c r="BR50" s="90"/>
+      <c r="BS50" s="90"/>
+      <c r="BT50" s="90"/>
+      <c r="BU50" s="90"/>
+      <c r="BV50" s="90"/>
+      <c r="BW50" s="90"/>
+      <c r="BX50" s="90"/>
+      <c r="BY50" s="90"/>
+      <c r="BZ50" s="90"/>
+      <c r="CA50" s="90"/>
+      <c r="CB50" s="90"/>
+      <c r="CC50" s="90"/>
+      <c r="CD50" s="90"/>
+      <c r="CE50" s="90"/>
+      <c r="CF50" s="90"/>
+      <c r="CG50" s="90"/>
+      <c r="CH50" s="90"/>
+      <c r="CI50" s="90"/>
+      <c r="CJ50" s="90"/>
+      <c r="CK50" s="90"/>
+      <c r="CL50" s="90"/>
+      <c r="CM50" s="90"/>
+      <c r="CN50" s="91"/>
     </row>
     <row r="51" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A51" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A52" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:92" x14ac:dyDescent="0.45">
@@ -15096,17 +15089,17 @@
     </row>
     <row r="54" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A54" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="55" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A55" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A56" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B56" s="18"/>
     </row>
@@ -15117,21 +15110,34 @@
     </row>
     <row r="58" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A58" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:92" ht="14.25" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A59" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:92" ht="14.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A60" s="62" t="s">
-        <v>92</v>
+      <c r="A60" s="40" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="BK1:CN1"/>
+    <mergeCell ref="BK2:CN2"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="C2:AF2"/>
+    <mergeCell ref="C1:AF1"/>
+    <mergeCell ref="AG1:BJ1"/>
+    <mergeCell ref="AG2:BJ2"/>
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="E46:E50"/>
+    <mergeCell ref="I46:I50"/>
+    <mergeCell ref="K46:K50"/>
+    <mergeCell ref="O46:O50"/>
     <mergeCell ref="BK46:CN50"/>
     <mergeCell ref="AW46:AW50"/>
     <mergeCell ref="AX46:AX50"/>
@@ -15140,19 +15146,6 @@
     <mergeCell ref="AO46:AO50"/>
     <mergeCell ref="AS46:AS50"/>
     <mergeCell ref="AU46:AU50"/>
-    <mergeCell ref="A46:A50"/>
-    <mergeCell ref="E46:E50"/>
-    <mergeCell ref="I46:I50"/>
-    <mergeCell ref="K46:K50"/>
-    <mergeCell ref="O46:O50"/>
-    <mergeCell ref="BK1:CN1"/>
-    <mergeCell ref="BK2:CN2"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="C2:AF2"/>
-    <mergeCell ref="C1:AF1"/>
-    <mergeCell ref="AG1:BJ1"/>
-    <mergeCell ref="AG2:BJ2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
